--- a/Backtest/06-01-23/S&P500stock_06-01-23period252RS90.xlsx
+++ b/Backtest/06-01-23/S&P500stock_06-01-23period252RS90.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="76">
   <si>
     <t>Stock</t>
   </si>
@@ -127,25 +127,121 @@
     <t>EM Rating</t>
   </si>
   <si>
-    <t>HES</t>
-  </si>
-  <si>
-    <t>SLB</t>
-  </si>
-  <si>
-    <t>2023-01-25</t>
-  </si>
-  <si>
-    <t>2023-01-20</t>
-  </si>
-  <si>
-    <t>Energy</t>
-  </si>
-  <si>
-    <t>Oil &amp; Gas E&amp;P</t>
-  </si>
-  <si>
-    <t>Oil &amp; Gas Equipment &amp; Services</t>
+    <t>GE</t>
+  </si>
+  <si>
+    <t>LW</t>
+  </si>
+  <si>
+    <t>PCG</t>
+  </si>
+  <si>
+    <t>CAH</t>
+  </si>
+  <si>
+    <t>RCL</t>
+  </si>
+  <si>
+    <t>PLTR</t>
+  </si>
+  <si>
+    <t>UBER</t>
+  </si>
+  <si>
+    <t>ANET</t>
+  </si>
+  <si>
+    <t>AVGO</t>
+  </si>
+  <si>
+    <t>ROK</t>
+  </si>
+  <si>
+    <t>DECK</t>
+  </si>
+  <si>
+    <t>CMG</t>
+  </si>
+  <si>
+    <t>MV</t>
+  </si>
+  <si>
+    <t>2023-07-25</t>
+  </si>
+  <si>
+    <t>2023-07-27</t>
+  </si>
+  <si>
+    <t>2023-08-15</t>
+  </si>
+  <si>
+    <t>2023-08-07</t>
+  </si>
+  <si>
+    <t>2023-08-01</t>
+  </si>
+  <si>
+    <t>2023-07-31</t>
+  </si>
+  <si>
+    <t>2023-08-31</t>
+  </si>
+  <si>
+    <t>2023-07-26</t>
+  </si>
+  <si>
+    <t>Industrials</t>
+  </si>
+  <si>
+    <t>Consumer Defensive</t>
+  </si>
+  <si>
+    <t>Utilities</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
+  </si>
+  <si>
+    <t>Consumer Cyclical</t>
+  </si>
+  <si>
+    <t>Technology</t>
+  </si>
+  <si>
+    <t>Aerospace &amp; Defense</t>
+  </si>
+  <si>
+    <t>Packaged Foods</t>
+  </si>
+  <si>
+    <t>Utilities - Regulated Electric</t>
+  </si>
+  <si>
+    <t>Medical Distribution</t>
+  </si>
+  <si>
+    <t>Travel Services</t>
+  </si>
+  <si>
+    <t>Software - Infrastructure</t>
+  </si>
+  <si>
+    <t>Software - Application</t>
+  </si>
+  <si>
+    <t>Computer Hardware</t>
+  </si>
+  <si>
+    <t>Semiconductors</t>
+  </si>
+  <si>
+    <t>Specialty Industrial Machinery</t>
+  </si>
+  <si>
+    <t>Footwear &amp; Accessories</t>
+  </si>
+  <si>
+    <t>Restaurants</t>
   </si>
 </sst>
 </file>
@@ -503,7 +599,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AK3"/>
+  <dimension ref="A1:AK13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:37">
@@ -624,46 +720,46 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>99.59839357429718</v>
+        <v>98.19277108433735</v>
       </c>
       <c r="C2">
-        <v>318</v>
+        <v>87</v>
       </c>
       <c r="D2">
-        <v>140.78</v>
+        <v>81.03</v>
       </c>
       <c r="E2">
-        <v>2.66</v>
+        <v>1.4</v>
       </c>
       <c r="F2">
-        <v>-0.7071067811865476</v>
+        <v>-0.5209202967876158</v>
       </c>
       <c r="G2">
-        <v>2.61</v>
+        <v>1.57</v>
       </c>
       <c r="H2">
-        <v>-0.7071067811865476</v>
+        <v>-0.585500215956691</v>
       </c>
       <c r="I2">
-        <v>138.9100036621094</v>
+        <v>81.2721450805664</v>
       </c>
       <c r="J2">
-        <v>136.8105010986328</v>
+        <v>81.06105346679688</v>
       </c>
       <c r="K2">
-        <v>140.6008001708984</v>
+        <v>78.31237030029297</v>
       </c>
       <c r="L2">
-        <v>120.1351498794556</v>
+        <v>60.07351791381836</v>
       </c>
       <c r="M2">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="N2">
-        <v>0.99</v>
+        <v>1.04</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -675,58 +771,58 @@
         <v>0</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="U2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W2" t="b">
         <v>0</v>
       </c>
       <c r="X2">
-        <v>80.5</v>
+        <v>37.34</v>
       </c>
       <c r="Y2">
-        <v>149.83</v>
+        <v>84.55</v>
       </c>
       <c r="Z2">
-        <v>33.67</v>
+        <v>83.7</v>
       </c>
       <c r="AA2">
-        <v>-0.14</v>
+        <v>-2.08</v>
       </c>
       <c r="AB2">
-        <v>297.37</v>
+        <v>248.03</v>
       </c>
       <c r="AC2">
-        <v>91.95</v>
+        <v>886.05</v>
       </c>
       <c r="AD2">
-        <v>7.4</v>
+        <v>18.96</v>
       </c>
       <c r="AE2">
-        <v>-22.33</v>
+        <v>253.93</v>
       </c>
       <c r="AF2">
-        <v>59.26</v>
+        <v>2287.5</v>
       </c>
       <c r="AG2">
-        <v>55.17</v>
+        <v>109.3</v>
       </c>
       <c r="AH2" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="AI2" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="AJ2" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="AK2">
-        <v>90.00000000000001</v>
+        <v>91.25</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -734,40 +830,40 @@
         <v>38</v>
       </c>
       <c r="B3">
-        <v>98.39357429718876</v>
+        <v>97.99196787148594</v>
       </c>
       <c r="C3">
-        <v>64</v>
+        <v>312</v>
       </c>
       <c r="D3">
-        <v>52.67</v>
+        <v>111.2</v>
       </c>
       <c r="E3">
-        <v>2.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F3">
-        <v>0.7071067811865476</v>
+        <v>-0.8050586404899516</v>
       </c>
       <c r="G3">
-        <v>2.78</v>
+        <v>0.98</v>
       </c>
       <c r="H3">
-        <v>0.7071067811865476</v>
+        <v>-1.150260642247341</v>
       </c>
       <c r="I3">
-        <v>52.44799957275391</v>
+        <v>109.6359985351562</v>
       </c>
       <c r="J3">
-        <v>51.2189998626709</v>
+        <v>111.8689998626709</v>
       </c>
       <c r="K3">
-        <v>51.93439987182617</v>
+        <v>108.7003999328613</v>
       </c>
       <c r="L3">
-        <v>42.68660002708435</v>
+        <v>93.57720005035401</v>
       </c>
       <c r="M3">
-        <v>1.02</v>
+        <v>0.98</v>
       </c>
       <c r="N3">
         <v>1.01</v>
@@ -779,64 +875,1170 @@
         <v>0</v>
       </c>
       <c r="R3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>4.444444444444444</v>
+        <v>0</v>
       </c>
       <c r="U3" t="b">
         <v>1</v>
       </c>
       <c r="V3" t="b">
+        <v>0</v>
+      </c>
+      <c r="W3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>62.62</v>
+      </c>
+      <c r="Y3">
+        <v>115.31</v>
+      </c>
+      <c r="Z3">
+        <v>14.57</v>
+      </c>
+      <c r="AA3">
+        <v>6.72</v>
+      </c>
+      <c r="AB3">
+        <v>106.01</v>
+      </c>
+      <c r="AC3">
+        <v>454.55</v>
+      </c>
+      <c r="AD3">
+        <v>24.5</v>
+      </c>
+      <c r="AE3">
+        <v>69.44</v>
+      </c>
+      <c r="AF3">
+        <v>-55.28</v>
+      </c>
+      <c r="AG3">
+        <v>631.8200000000001</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>59</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK3">
+        <v>72.14751848439028</v>
+      </c>
+    </row>
+    <row r="4" spans="1:37">
+      <c r="A4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4">
+        <v>93.37349397590361</v>
+      </c>
+      <c r="C4">
+        <v>24</v>
+      </c>
+      <c r="D4">
+        <v>16.94</v>
+      </c>
+      <c r="E4">
+        <v>0.89</v>
+      </c>
+      <c r="F4">
+        <v>-0.8359432430662923</v>
+      </c>
+      <c r="G4">
+        <v>1.08</v>
+      </c>
+      <c r="H4">
+        <v>-1.054538536096383</v>
+      </c>
+      <c r="I4">
+        <v>16.60200004577637</v>
+      </c>
+      <c r="J4">
+        <v>16.92450017929077</v>
+      </c>
+      <c r="K4">
+        <v>16.69040002822876</v>
+      </c>
+      <c r="L4">
+        <v>15.26490000724792</v>
+      </c>
+      <c r="M4">
+        <v>0.98</v>
+      </c>
+      <c r="N4">
+        <v>0.99</v>
+      </c>
+      <c r="P4">
         <v>1</v>
       </c>
-      <c r="W3" t="b">
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0.5555555555555555</v>
+      </c>
+      <c r="U4" t="b">
         <v>1</v>
       </c>
-      <c r="X3">
-        <v>30.65</v>
-      </c>
-      <c r="Y3">
-        <v>56.04</v>
-      </c>
-      <c r="Z3">
-        <v>51.66</v>
-      </c>
-      <c r="AA3">
-        <v>-25.36</v>
-      </c>
-      <c r="AB3">
-        <v>30.25</v>
-      </c>
-      <c r="AC3">
-        <v>48.84</v>
-      </c>
-      <c r="AD3">
-        <v>5.25</v>
-      </c>
-      <c r="AE3">
-        <v>-5.88</v>
-      </c>
-      <c r="AF3">
-        <v>88.89</v>
-      </c>
-      <c r="AG3">
-        <v>-16.28</v>
-      </c>
-      <c r="AH3" t="s">
+      <c r="V4" t="b">
+        <v>1</v>
+      </c>
+      <c r="W4" t="b">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>9.640000000000001</v>
+      </c>
+      <c r="Y4">
+        <v>17.68</v>
+      </c>
+      <c r="Z4">
+        <v>34.47</v>
+      </c>
+      <c r="AA4">
+        <v>18.1</v>
+      </c>
+      <c r="AB4">
+        <v>209.68</v>
+      </c>
+      <c r="AC4">
+        <v>61.11</v>
+      </c>
+      <c r="AD4">
+        <v>2.43</v>
+      </c>
+      <c r="AE4">
+        <v>11.54</v>
+      </c>
+      <c r="AF4">
+        <v>13.04</v>
+      </c>
+      <c r="AG4">
+        <v>27.78</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>60</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>66</v>
+      </c>
+      <c r="AK4">
+        <v>71.96580398948016</v>
+      </c>
+    </row>
+    <row r="5" spans="1:37">
+      <c r="A5" t="s">
         <v>40</v>
       </c>
-      <c r="AI3" t="s">
+      <c r="B5">
+        <v>94.37751004016064</v>
+      </c>
+      <c r="C5">
+        <v>248</v>
+      </c>
+      <c r="D5">
+        <v>82.3</v>
+      </c>
+      <c r="E5">
+        <v>1.2</v>
+      </c>
+      <c r="F5">
+        <v>-0.6444587070929791</v>
+      </c>
+      <c r="G5">
+        <v>1.36</v>
+      </c>
+      <c r="H5">
+        <v>-0.786516638873702</v>
+      </c>
+      <c r="I5">
+        <v>83.2240005493164</v>
+      </c>
+      <c r="J5">
+        <v>84.25099983215333</v>
+      </c>
+      <c r="K5">
+        <v>80.35159988403321</v>
+      </c>
+      <c r="L5">
+        <v>75.80980014801025</v>
+      </c>
+      <c r="M5">
+        <v>0.99</v>
+      </c>
+      <c r="N5">
+        <v>1.04</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="b">
+        <v>0</v>
+      </c>
+      <c r="W5" t="b">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>49.7</v>
+      </c>
+      <c r="Y5">
+        <v>87.03</v>
+      </c>
+      <c r="Z5">
+        <v>19.48</v>
+      </c>
+      <c r="AA5">
+        <v>12.97</v>
+      </c>
+      <c r="AB5">
+        <v>161.62</v>
+      </c>
+      <c r="AC5">
+        <v>136.84</v>
+      </c>
+      <c r="AD5">
+        <v>-15.64</v>
+      </c>
+      <c r="AE5">
+        <v>370</v>
+      </c>
+      <c r="AF5">
+        <v>-221.95</v>
+      </c>
+      <c r="AG5">
+        <v>-28.07</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>67</v>
+      </c>
+      <c r="AK5">
+        <v>71.86204462031205</v>
+      </c>
+    </row>
+    <row r="6" spans="1:37">
+      <c r="A6" t="s">
         <v>41</v>
       </c>
-      <c r="AJ3" t="s">
+      <c r="B6">
+        <v>93.77510040160642</v>
+      </c>
+      <c r="C6">
+        <v>225</v>
+      </c>
+      <c r="D6">
+        <v>80.97</v>
+      </c>
+      <c r="E6">
+        <v>2.48</v>
+      </c>
+      <c r="F6">
+        <v>0.1461871188613465</v>
+      </c>
+      <c r="G6">
+        <v>2.66</v>
+      </c>
+      <c r="H6">
+        <v>0.4578707410887476</v>
+      </c>
+      <c r="I6">
+        <v>79.0780014038086</v>
+      </c>
+      <c r="J6">
+        <v>77.24850006103516</v>
+      </c>
+      <c r="K6">
+        <v>68.64720008850098</v>
+      </c>
+      <c r="L6">
+        <v>58.81780004501343</v>
+      </c>
+      <c r="M6">
+        <v>1.02</v>
+      </c>
+      <c r="N6">
+        <v>1.15</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>1</v>
+      </c>
+      <c r="V6" t="b">
+        <v>1</v>
+      </c>
+      <c r="W6" t="b">
+        <v>1</v>
+      </c>
+      <c r="X6">
+        <v>31.09</v>
+      </c>
+      <c r="Y6">
+        <v>81.16</v>
+      </c>
+      <c r="Z6">
+        <v>16.65</v>
+      </c>
+      <c r="AA6">
+        <v>-0.85</v>
+      </c>
+      <c r="AB6">
+        <v>82.23999999999999</v>
+      </c>
+      <c r="AC6">
+        <v>90.73</v>
+      </c>
+      <c r="AD6">
+        <v>-1.59</v>
+      </c>
+      <c r="AE6">
+        <v>90.26000000000001</v>
+      </c>
+      <c r="AF6">
+        <v>-1600</v>
+      </c>
+      <c r="AG6">
+        <v>106.34</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>51</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>62</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK6">
+        <v>58.43243450847967</v>
+      </c>
+    </row>
+    <row r="7" spans="1:37">
+      <c r="A7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7">
+        <v>98.39357429718876</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>14.71</v>
+      </c>
+      <c r="E7">
+        <v>6.55</v>
+      </c>
+      <c r="F7">
+        <v>2.660193768575491</v>
+      </c>
+      <c r="G7">
+        <v>4.68</v>
+      </c>
+      <c r="H7">
+        <v>2.391457285338092</v>
+      </c>
+      <c r="I7">
+        <v>13.62799987792969</v>
+      </c>
+      <c r="J7">
+        <v>10.71349999904633</v>
+      </c>
+      <c r="K7">
+        <v>9.21420000076294</v>
+      </c>
+      <c r="L7">
+        <v>8.105350008010864</v>
+      </c>
+      <c r="M7">
+        <v>1.27</v>
+      </c>
+      <c r="N7">
+        <v>1.48</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="b">
+        <v>1</v>
+      </c>
+      <c r="W7" t="b">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>5.92</v>
+      </c>
+      <c r="Y7">
+        <v>15.01</v>
+      </c>
+      <c r="Z7">
+        <v>18.74</v>
+      </c>
+      <c r="AA7">
+        <v>1.13</v>
+      </c>
+      <c r="AB7">
+        <v>64.70999999999999</v>
+      </c>
+      <c r="AC7">
+        <v>111.11</v>
+      </c>
+      <c r="AD7">
+        <v>0.68</v>
+      </c>
+      <c r="AE7">
+        <v>-50</v>
+      </c>
+      <c r="AF7">
+        <v>133.33</v>
+      </c>
+      <c r="AG7">
+        <v>33.33</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>69</v>
+      </c>
+      <c r="AK7">
+        <v>55.75170345088475</v>
+      </c>
+    </row>
+    <row r="8" spans="1:37">
+      <c r="A8" t="s">
         <v>43</v>
       </c>
-      <c r="AK3">
-        <v>10</v>
+      <c r="B8">
+        <v>97.59036144578313</v>
+      </c>
+      <c r="C8">
+        <v>29</v>
+      </c>
+      <c r="D8">
+        <v>37.93</v>
+      </c>
+      <c r="E8">
+        <v>1.78</v>
+      </c>
+      <c r="F8">
+        <v>-0.2861973172074253</v>
+      </c>
+      <c r="G8">
+        <v>2.64</v>
+      </c>
+      <c r="H8">
+        <v>0.4387263198585561</v>
+      </c>
+      <c r="I8">
+        <v>37.97000045776367</v>
+      </c>
+      <c r="J8">
+        <v>38.26450004577637</v>
+      </c>
+      <c r="K8">
+        <v>34.11420021057129</v>
+      </c>
+      <c r="L8">
+        <v>30.62850008010864</v>
+      </c>
+      <c r="M8">
+        <v>0.99</v>
+      </c>
+      <c r="N8">
+        <v>1.11</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8" t="b">
+        <v>1</v>
+      </c>
+      <c r="V8" t="b">
+        <v>0</v>
+      </c>
+      <c r="W8" t="b">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>19.9</v>
+      </c>
+      <c r="Y8">
+        <v>40.5</v>
+      </c>
+      <c r="Z8">
+        <v>63.7</v>
+      </c>
+      <c r="AA8">
+        <v>-338000</v>
+      </c>
+      <c r="AB8">
+        <v>62.86</v>
+      </c>
+      <c r="AC8">
+        <v>93.94</v>
+      </c>
+      <c r="AD8">
+        <v>-1.9</v>
+      </c>
+      <c r="AE8">
+        <v>-125</v>
+      </c>
+      <c r="AF8">
+        <v>152.46</v>
+      </c>
+      <c r="AG8">
+        <v>53.79</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>54</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK8">
+        <v>54.28802587165019</v>
+      </c>
+    </row>
+    <row r="9" spans="1:37">
+      <c r="A9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9">
+        <v>97.18875502008032</v>
+      </c>
+      <c r="C9">
+        <v>22</v>
+      </c>
+      <c r="D9">
+        <v>41.58</v>
+      </c>
+      <c r="E9">
+        <v>3.62</v>
+      </c>
+      <c r="F9">
+        <v>0.8503560576019178</v>
+      </c>
+      <c r="G9">
+        <v>3.35</v>
+      </c>
+      <c r="H9">
+        <v>1.118353273530355</v>
+      </c>
+      <c r="I9">
+        <v>40.42649993896485</v>
+      </c>
+      <c r="J9">
+        <v>36.14012508392334</v>
+      </c>
+      <c r="K9">
+        <v>38.65420021057129</v>
+      </c>
+      <c r="L9">
+        <v>33.2590500831604</v>
+      </c>
+      <c r="M9">
+        <v>1.12</v>
+      </c>
+      <c r="N9">
+        <v>1.05</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>2</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>4</v>
+      </c>
+      <c r="T9">
+        <v>8.888888888888888</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" t="b">
+        <v>1</v>
+      </c>
+      <c r="W9" t="b">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>22.28</v>
+      </c>
+      <c r="Y9">
+        <v>44.59</v>
+      </c>
+      <c r="Z9">
+        <v>13.24</v>
+      </c>
+      <c r="AA9">
+        <v>76.18000000000001</v>
+      </c>
+      <c r="AB9">
+        <v>23.44</v>
+      </c>
+      <c r="AC9">
+        <v>44.9</v>
+      </c>
+      <c r="AD9">
+        <v>8.19</v>
+      </c>
+      <c r="AE9">
+        <v>2.16</v>
+      </c>
+      <c r="AF9">
+        <v>19.83</v>
+      </c>
+      <c r="AG9">
+        <v>18.37</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>55</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>71</v>
+      </c>
+      <c r="AK9">
+        <v>44.17306192803295</v>
+      </c>
+    </row>
+    <row r="10" spans="1:37">
+      <c r="A10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10">
+        <v>93.57429718875501</v>
+      </c>
+      <c r="C10">
+        <v>8</v>
+      </c>
+      <c r="D10">
+        <v>80.8</v>
+      </c>
+      <c r="E10">
+        <v>3.1</v>
+      </c>
+      <c r="F10">
+        <v>0.529156190807973</v>
+      </c>
+      <c r="G10">
+        <v>2.18</v>
+      </c>
+      <c r="H10">
+        <v>-0.001595368435849119</v>
+      </c>
+      <c r="I10">
+        <v>76.64720001220704</v>
+      </c>
+      <c r="J10">
+        <v>67.41114978790283</v>
+      </c>
+      <c r="K10">
+        <v>64.6872998046875</v>
+      </c>
+      <c r="L10">
+        <v>56.37997495651245</v>
+      </c>
+      <c r="M10">
+        <v>1.14</v>
+      </c>
+      <c r="N10">
+        <v>1.18</v>
+      </c>
+      <c r="O10" t="s">
+        <v>14</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>1</v>
+      </c>
+      <c r="T10">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="U10" t="b">
+        <v>0</v>
+      </c>
+      <c r="V10" t="b">
+        <v>1</v>
+      </c>
+      <c r="W10" t="b">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>41.51</v>
+      </c>
+      <c r="Y10">
+        <v>92.18000000000001</v>
+      </c>
+      <c r="Z10">
+        <v>250.97</v>
+      </c>
+      <c r="AA10">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="AB10">
+        <v>25.2</v>
+      </c>
+      <c r="AC10">
+        <v>46.59</v>
+      </c>
+      <c r="AD10">
+        <v>16.19</v>
+      </c>
+      <c r="AE10">
+        <v>12.03</v>
+      </c>
+      <c r="AF10">
+        <v>8.92</v>
+      </c>
+      <c r="AG10">
+        <v>20.13</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AK10">
+        <v>37.40586487814984</v>
+      </c>
+    </row>
+    <row r="11" spans="1:37">
+      <c r="A11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11">
+        <v>91.76706827309236</v>
+      </c>
+      <c r="C11">
+        <v>423</v>
+      </c>
+      <c r="D11">
+        <v>278.6</v>
+      </c>
+      <c r="E11">
+        <v>1.87</v>
+      </c>
+      <c r="F11">
+        <v>-0.2306050325700117</v>
+      </c>
+      <c r="G11">
+        <v>1.93</v>
+      </c>
+      <c r="H11">
+        <v>-0.2409006338132435</v>
+      </c>
+      <c r="I11">
+        <v>279.05400390625</v>
+      </c>
+      <c r="J11">
+        <v>277.4960021972656</v>
+      </c>
+      <c r="K11">
+        <v>278.4744006347656</v>
+      </c>
+      <c r="L11">
+        <v>264.8454502105713</v>
+      </c>
+      <c r="M11">
+        <v>1.01</v>
+      </c>
+      <c r="N11">
+        <v>1</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11" t="b">
+        <v>0</v>
+      </c>
+      <c r="V11" t="b">
+        <v>0</v>
+      </c>
+      <c r="W11" t="b">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>190.08</v>
+      </c>
+      <c r="Y11">
+        <v>309.36</v>
+      </c>
+      <c r="Z11">
+        <v>33.92</v>
+      </c>
+      <c r="AA11">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="AB11">
+        <v>40.69</v>
+      </c>
+      <c r="AC11">
+        <v>1.56</v>
+      </c>
+      <c r="AD11">
+        <v>8.58</v>
+      </c>
+      <c r="AE11">
+        <v>-21.92</v>
+      </c>
+      <c r="AF11">
+        <v>14.04</v>
+      </c>
+      <c r="AG11">
+        <v>14.06</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>54</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>58</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>73</v>
+      </c>
+      <c r="AK11">
+        <v>25.66314622602249</v>
+      </c>
+    </row>
+    <row r="12" spans="1:37">
+      <c r="A12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12">
+        <v>98.79518072289156</v>
+      </c>
+      <c r="C12">
+        <v>89</v>
+      </c>
+      <c r="D12">
+        <v>79.17</v>
+      </c>
+      <c r="E12">
+        <v>2.23</v>
+      </c>
+      <c r="F12">
+        <v>-0.008235894020357749</v>
+      </c>
+      <c r="G12">
+        <v>1.85</v>
+      </c>
+      <c r="H12">
+        <v>-0.3174783187340095</v>
+      </c>
+      <c r="I12">
+        <v>77.32133178710937</v>
+      </c>
+      <c r="J12">
+        <v>79.20333328247071</v>
+      </c>
+      <c r="K12">
+        <v>77.93906616210937</v>
+      </c>
+      <c r="L12">
+        <v>66.24206649780274</v>
+      </c>
+      <c r="M12">
+        <v>0.98</v>
+      </c>
+      <c r="N12">
+        <v>0.99</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12" t="b">
+        <v>0</v>
+      </c>
+      <c r="V12" t="b">
+        <v>1</v>
+      </c>
+      <c r="W12" t="b">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>39.74</v>
+      </c>
+      <c r="Y12">
+        <v>83.91</v>
+      </c>
+      <c r="Z12">
+        <v>12</v>
+      </c>
+      <c r="AA12">
+        <v>346.2</v>
+      </c>
+      <c r="AB12">
+        <v>7.73</v>
+      </c>
+      <c r="AC12">
+        <v>106.61</v>
+      </c>
+      <c r="AD12">
+        <v>5.2</v>
+      </c>
+      <c r="AE12">
+        <v>-67.3</v>
+      </c>
+      <c r="AF12">
+        <v>175.47</v>
+      </c>
+      <c r="AG12">
+        <v>129.36</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>51</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>62</v>
+      </c>
+      <c r="AJ12" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK12">
+        <v>22.37518655457368</v>
+      </c>
+    </row>
+    <row r="13" spans="1:37">
+      <c r="A13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13">
+        <v>96.3855421686747</v>
+      </c>
+      <c r="C13">
+        <v>36</v>
+      </c>
+      <c r="D13">
+        <v>41.53</v>
+      </c>
+      <c r="E13">
+        <v>0.86</v>
+      </c>
+      <c r="F13">
+        <v>-0.854474004612097</v>
+      </c>
+      <c r="G13">
+        <v>1.9</v>
+      </c>
+      <c r="H13">
+        <v>-0.2696172656585308</v>
+      </c>
+      <c r="I13">
+        <v>41.31903991699219</v>
+      </c>
+      <c r="J13">
+        <v>41.18446006774902</v>
+      </c>
+      <c r="K13">
+        <v>37.66525993347168</v>
+      </c>
+      <c r="L13">
+        <v>32.6837620639801</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
+        <v>1.1</v>
+      </c>
+      <c r="O13" t="s">
+        <v>49</v>
+      </c>
+      <c r="P13">
+        <v>3</v>
+      </c>
+      <c r="Q13">
+        <v>4</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>6.111111111111111</v>
+      </c>
+      <c r="U13" t="b">
+        <v>1</v>
+      </c>
+      <c r="V13" t="b">
+        <v>1</v>
+      </c>
+      <c r="W13" t="b">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>23.93</v>
+      </c>
+      <c r="Y13">
+        <v>42.8</v>
+      </c>
+      <c r="Z13">
+        <v>47.47</v>
+      </c>
+      <c r="AA13">
+        <v>525.96</v>
+      </c>
+      <c r="AB13">
+        <v>10.55</v>
+      </c>
+      <c r="AC13">
+        <v>13.3</v>
+      </c>
+      <c r="AD13">
+        <v>11.75</v>
+      </c>
+      <c r="AE13">
+        <v>31.02</v>
+      </c>
+      <c r="AF13">
+        <v>-12.96</v>
+      </c>
+      <c r="AG13">
+        <v>-0.64</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>57</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>62</v>
+      </c>
+      <c r="AJ13" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK13">
+        <v>21.76540838582299</v>
       </c>
     </row>
   </sheetData>
